--- a/entrepreneur_forms/004_housing_technology_incubator_registration_form--entrepreneur_forms.xlsx
+++ b/entrepreneur_forms/004_housing_technology_incubator_registration_form--entrepreneur_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Signature Date</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>tech_stack</t>
+          <t>tech_stack_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>funding_info</t>
+          <t>funding_info_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>file_upload</t>
+          <t>file_upload_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>File Upload 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tech_stack_choices</t>
+          <t>tech_stack_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>funding_info_choices</t>
+          <t>funding_info_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>funding_info_choices</t>
+          <t>funding_info_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>funding_info_choices</t>
+          <t>funding_info_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>funding_info_choices</t>
+          <t>funding_info_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>funding_info_choices</t>
+          <t>funding_info_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>funding_info_choices</t>
+          <t>funding_info_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>location_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>location_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>location_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>location_choices</t>
+          <t>location_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
